--- a/docs/1_打疫苗时间/打疫苗时间.xlsx
+++ b/docs/1_打疫苗时间/打疫苗时间.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055"/>
+    <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>时间</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF080808"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>13</t>
     </r>
     <r>
@@ -129,6 +135,12 @@
   </si>
   <si>
     <t>2月整    (8月17号)</t>
+  </si>
+  <si>
+    <t>2月+20天 (9月6号)</t>
+  </si>
+  <si>
+    <t>口服第2次</t>
   </si>
 </sst>
 </file>
@@ -789,14 +801,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1123,17 +1132,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.6548672566372" customWidth="1"/>
-    <col min="2" max="2" width="10.9823008849558" customWidth="1"/>
-    <col min="3" max="3" width="10.2477876106195" customWidth="1"/>
-    <col min="4" max="4" width="10.2920353982301" customWidth="1"/>
-    <col min="5" max="5" width="10.2477876106195" customWidth="1"/>
-    <col min="6" max="8" width="9.76106194690266" customWidth="1"/>
+    <col min="1" max="1" width="21.6574074074074" customWidth="1"/>
+    <col min="2" max="2" width="7.66666666666667" customWidth="1"/>
+    <col min="3" max="3" width="8.81481481481481" customWidth="1"/>
+    <col min="4" max="4" width="7.42592592592593" customWidth="1"/>
+    <col min="5" max="5" width="11.2592592592593" customWidth="1"/>
+    <col min="6" max="8" width="9.75925925925926" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:8">
+    <row r="1" ht="15.6" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,220 +1155,224 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1372,7 +1385,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1384,7 +1397,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/1_打疫苗时间/打疫苗时间.xlsx
+++ b/docs/1_打疫苗时间/打疫苗时间.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500"/>
+    <workbookView windowWidth="24000" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>时间</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>口服第2次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         (9月17号)</t>
+  </si>
+  <si>
+    <t>第2针脊灰和第1针四联的照片:</t>
   </si>
 </sst>
 </file>
@@ -879,6 +885,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>642620</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>549275</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>106045</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7466330" y="1397000"/>
+          <a:ext cx="3135630" cy="4566920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1131,18 +1184,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="21.6574074074074" customWidth="1"/>
-    <col min="2" max="2" width="7.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="8.81481481481481" customWidth="1"/>
-    <col min="4" max="4" width="7.42592592592593" customWidth="1"/>
-    <col min="5" max="5" width="11.2592592592593" customWidth="1"/>
-    <col min="6" max="8" width="9.75925925925926" customWidth="1"/>
+    <col min="1" max="1" width="21.6548672566372" customWidth="1"/>
+    <col min="2" max="2" width="7.66371681415929" customWidth="1"/>
+    <col min="3" max="3" width="8.8141592920354" customWidth="1"/>
+    <col min="4" max="4" width="7.42477876106195" customWidth="1"/>
+    <col min="5" max="5" width="11.2566371681416" customWidth="1"/>
+    <col min="6" max="8" width="9.76106194690266" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:8">
+    <row r="1" ht="15.75" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,15 +1307,24 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="4"/>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="5"/>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4"/>
@@ -1378,6 +1440,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1385,7 +1448,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1397,7 +1460,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
